--- a/docs/ljh/API 명세서.xlsx
+++ b/docs/ljh/API 명세서.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KDT\git\mjc_b-hotel-reservation\docs\phi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca904c52f6ffc0d5/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48EC98DE-EB3C-4A0F-B92B-9B23EF2676DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{48EC98DE-EB3C-4A0F-B92B-9B23EF2676DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ABB5124-BC55-43F1-859A-94FCF4BA345B}"/>
   <bookViews>
-    <workbookView xWindow="2242" yWindow="322" windowWidth="16485" windowHeight="12136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="72">
   <si>
     <t>화면ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,6 +76,242 @@
   </si>
   <si>
     <t>회원가입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>p</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>담당자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행률</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍길동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이재현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/sales/dashboard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/sales/monthly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/sales/top-bookings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/sales/rooms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hotelId (Long), targetMonth (String)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	해당 호텔 매출 분석 대시보드 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADMIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SalesDashboardResponse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hotelId (Long), startDate (String)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 월별 매출 추이 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonthlyRevenueDto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 매출 TOP 5 예약 내역 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;List&lt;TopBookingDto&gt;&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 객실 유형별 통계 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;List&lt;RoomTypeRevenueDto&gt;&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/hotels/{hotelId}/summary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요청 데이터: hotelId (Long, Path Variable)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RateSummaryResponseDto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 요금/시즌 요약 정보 조회</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>PUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/{seasonRateld}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SeasonRateDto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seasonRateId - Path Variable
+SeasonRateDto - Request Body
+multiplier - Query Parameter (선택, 기본값 20.0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔의 시즌 요금 정보 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DELETE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/preview</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/hotels/{hotelId}/rooms/{roomType}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔의 시즌 요금 정보 삭제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seasonRateId - Path Variable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔의 시즌 요금 정보 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SeasonRateDto - Request Body, multiplier - Query Parameter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PricePreviewDto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔의 요금 변경 미리보기(시뮬레이션) 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	previewDto (PricePreviewDto, Request Body)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hotelId (Long), roomType(String)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔의 특정 객실 유형 시즌 요금 목록 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;SeasonRateDto&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/policies/hotels/{hotelId}/times</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/policies/hotels/{hotelId}/min-stay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/policies/hotels/{hotelId}/child-rates</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/policies/hotels/{hotelId}/cancellation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/policies/hotels/{hotelId}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 체크인/체크아웃 시간 정책 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RatePolicyDto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hotelId - Path Variable, requestDto - Request Body</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 최소 투숙 박수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">해당 호텔 무료 아동 나이 및 아동 요금 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 취소 기한 및 취소 수수료율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hotelId - Path Variable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	해당 호텔 요금 정책 조회</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -83,7 +319,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +333,13 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -119,8 +362,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -401,17 +651,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="1.5625" customWidth="1"/>
-    <col min="3" max="3" width="15.5625" customWidth="1"/>
-    <col min="4" max="5" width="20.5625" customWidth="1"/>
-    <col min="6" max="6" width="15.5625" customWidth="1"/>
-    <col min="7" max="8" width="20.5625" customWidth="1"/>
+    <col min="1" max="1" width="3.9140625" customWidth="1"/>
+    <col min="3" max="3" width="15.58203125" customWidth="1"/>
+    <col min="4" max="4" width="39.9140625" customWidth="1"/>
+    <col min="5" max="5" width="53.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.58203125" customWidth="1"/>
+    <col min="7" max="7" width="44.9140625" customWidth="1"/>
+    <col min="8" max="8" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -433,8 +685,14 @@
       <c r="H1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -455,6 +713,407 @@
       </c>
       <c r="H2" t="b">
         <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="51" x14ac:dyDescent="0.45">
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>68</v>
+      </c>
+      <c r="H17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.45">
+      <c r="D28" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ljh/API 명세서.xlsx
+++ b/docs/ljh/API 명세서.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca904c52f6ffc0d5/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\mjc_b-hotel-reservation_doc\docs\ljh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{48EC98DE-EB3C-4A0F-B92B-9B23EF2676DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ABB5124-BC55-43F1-859A-94FCF4BA345B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E50CFA0-2D1E-44BB-8A33-D9876DEEDC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
   <si>
     <t>화면ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,10 +76,6 @@
   </si>
   <si>
     <t>회원가입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>p</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -651,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3.9140625" customWidth="1"/>
@@ -686,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
         <v>14</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
@@ -715,7 +711,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" s="1">
         <v>0.1</v>
@@ -723,25 +719,25 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
       <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3" s="1">
         <v>1</v>
@@ -749,25 +745,25 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
@@ -775,25 +771,25 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
         <v>30</v>
       </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
@@ -801,25 +797,25 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
         <v>32</v>
       </c>
-      <c r="H6" t="s">
-        <v>33</v>
-      </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
@@ -827,25 +823,25 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
         <v>35</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" t="s">
         <v>36</v>
       </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" t="s">
-        <v>37</v>
-      </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
@@ -853,25 +849,25 @@
     </row>
     <row r="9" spans="1:10" ht="51" x14ac:dyDescent="0.45">
       <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
@@ -879,25 +875,25 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
@@ -908,22 +904,22 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
@@ -934,22 +930,22 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
@@ -957,25 +953,25 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" t="s">
         <v>56</v>
       </c>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>57</v>
       </c>
-      <c r="H13" t="s">
-        <v>58</v>
-      </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -983,25 +979,25 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" t="s">
         <v>64</v>
       </c>
-      <c r="H15" t="s">
-        <v>65</v>
-      </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J15" s="1">
         <v>1</v>
@@ -1009,25 +1005,25 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" t="s">
         <v>66</v>
       </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" t="s">
-        <v>67</v>
-      </c>
       <c r="H16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" s="1">
         <v>1</v>
@@ -1035,25 +1031,25 @@
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J17" s="1">
         <v>1</v>
@@ -1061,25 +1057,25 @@
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J18" s="1">
         <v>1</v>
@@ -1087,33 +1083,28 @@
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" t="s">
         <v>70</v>
       </c>
-      <c r="F19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" t="s">
-        <v>71</v>
-      </c>
       <c r="H19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="D28" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ljh/API 명세서.xlsx
+++ b/docs/ljh/API 명세서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\mjc_b-hotel-reservation_doc\docs\ljh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E50CFA0-2D1E-44BB-8A33-D9876DEEDC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91879213-DBB3-4AB6-812A-56CD44CF249C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="550" yWindow="620" windowWidth="18150" windowHeight="14380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="57">
   <si>
     <t>화면ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -159,47 +159,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/api/rates</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/rates/hotels/{hotelId}/summary</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>요청 데이터: hotelId (Long, Path Variable)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RateSummaryResponseDto</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 호텔 요금/시즌 요약 정보 조회</t>
-  </si>
-  <si>
     <t>PUT</t>
-  </si>
-  <si>
-    <t>PUT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/rates/{seasonRateld}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SeasonRateDto</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seasonRateId - Path Variable
-SeasonRateDto - Request Body
-multiplier - Query Parameter (선택, 기본값 20.0)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 호텔의 시즌 요금 정보 수정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -207,107 +167,90 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/api/rates/preview</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/rates/hotels/{hotelId}/rooms/{roomType}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>없음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>해당 호텔의 시즌 요금 정보 삭제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seasonRateId - Path Variable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 호텔의 시즌 요금 정보 등록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SeasonRateDto - Request Body, multiplier - Query Parameter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PricePreviewDto</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 호텔의 요금 변경 미리보기(시뮬레이션) 조회</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">	previewDto (PricePreviewDto, Request Body)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hotelId (Long), roomType(String)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 호텔의 특정 객실 유형 시즌 요금 목록 조회</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;SeasonRateDto&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/rates/policies/hotels/{hotelId}/times</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/rates/policies/hotels/{hotelId}/min-stay</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/rates/policies/hotels/{hotelId}/child-rates</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/rates/policies/hotels/{hotelId}/cancellation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/rates/policies/hotels/{hotelId}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 호텔 체크인/체크아웃 시간 정책 수정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RatePolicyDto</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hotelId - Path Variable, requestDto - Request Body</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 호텔 최소 투숙 박수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">해당 호텔 무료 아동 나이 및 아동 요금 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 호텔 취소 기한 및 취소 수수료율</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hotelId - Path Variable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">	해당 호텔 요금 정책 조회</t>
+    <t>/api/rates/rooms/{roomId}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/hotels/{hotelId}/rooms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/rooms/{roomId}/images</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/rates/rooms/{roomId}/images/{imageId}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>roomId (Long)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>roomId (Long), imageId (Long)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 객실의 이미지 1개 삭제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔의 객실에 이미지 여러 장 추가 업로드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hotelId (Long)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	ApiResponse&lt;RoomDetailResponseDto&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 호실 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ApiResponse&lt;Page&lt;RoomListResponseDto&gt;&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 호실 목록을 페이지 단위로 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 호실 1개의 상세 정보 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 호텔 	호실 정보, 상세설명, 편의시설 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ApiResponse&lt;Void&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">해당 호텔 	호실을 삭제 처리 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;RoomImageResponseDto&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	roomId (Long), RoomUpdateRequestDto (body)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hotelId (Long), RoomCreateRequestDto (body)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -315,7 +258,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,13 +272,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.8000000000000007"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -358,15 +294,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -647,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3.9140625" customWidth="1"/>
@@ -656,7 +586,7 @@
     <col min="5" max="5" width="53.33203125" customWidth="1"/>
     <col min="6" max="6" width="15.58203125" customWidth="1"/>
     <col min="7" max="7" width="44.9140625" customWidth="1"/>
-    <col min="8" max="8" width="27.33203125" customWidth="1"/>
+    <col min="8" max="8" width="36.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -826,45 +756,45 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
         <v>36</v>
       </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="51" x14ac:dyDescent="0.45">
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
       <c r="G9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
@@ -875,22 +805,22 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C10" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
         <v>40</v>
       </c>
-      <c r="E10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
       <c r="G10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
+      </c>
+      <c r="H10" t="s">
+        <v>52</v>
       </c>
       <c r="I10" t="s">
         <v>16</v>
@@ -901,22 +831,22 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C11" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -930,180 +860,76 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" t="s">
         <v>54</v>
       </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" t="s">
-        <v>57</v>
-      </c>
-      <c r="I13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="1">
+      <c r="I14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="H15" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="I15" t="s">
         <v>16</v>
       </c>
       <c r="J15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.45">
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="1">
         <v>1</v>
       </c>
     </row>
